--- a/output/pdf_financials_xlsx/APXC.xlsx
+++ b/output/pdf_financials_xlsx/APXC.xlsx
@@ -431,6 +431,11 @@
   </sheetPr>
   <dimension ref="A1:C135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/APXC.xlsx
+++ b/output/pdf_financials_xlsx/APXC.xlsx
@@ -592,10 +592,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -644,10 +644,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">

--- a/output/pdf_financials_xlsx/APXC.xlsx
+++ b/output/pdf_financials_xlsx/APXC.xlsx
@@ -631,10 +631,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.500185</v>
+        <v>-0.500185</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>4.089117</v>
+        <v>-4.089117</v>
       </c>
     </row>
     <row r="17">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.500185</v>
+        <v>-0.500185</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>4.089117</v>
+        <v>-4.089117</v>
       </c>
     </row>
     <row r="21">
@@ -730,10 +730,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.500185</v>
+        <v>-0.500185</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>4.089117</v>
+        <v>-4.089117</v>
       </c>
     </row>
     <row r="24">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>25.00925</v>
+        <v>-25.00925</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>45.434633</v>
+        <v>-45.434633</v>
       </c>
     </row>
     <row r="27">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.500185</v>
+        <v>-0.500185</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>4.089117</v>
+        <v>-4.089117</v>
       </c>
     </row>
     <row r="28">
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.500185</v>
+        <v>-0.500185</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>4.089117</v>
+        <v>-4.089117</v>
       </c>
     </row>
     <row r="30">
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.115255</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.706549</v>
       </c>
     </row>
     <row r="93">
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.30794</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-1.018235</v>
       </c>
     </row>
     <row r="119">
@@ -2612,7 +2612,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="n">
         <v>0.115255</v>
       </c>
@@ -3062,7 +3066,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E31" s="5" t="n">
         <v>-0.30794</v>
       </c>
@@ -3646,10 +3654,10 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>0.500185</v>
+        <v>-0.500185</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>4.089117</v>
+        <v>-4.089117</v>
       </c>
     </row>
     <row r="54">

--- a/output/pdf_financials_xlsx/APXC.xlsx
+++ b/output/pdf_financials_xlsx/APXC.xlsx
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.002944</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.09933599999999999</v>
       </c>
     </row>
     <row r="13">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.500185</v>
+        <v>-0.503129</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-4.089117</v>
+        <v>-4.188453</v>
       </c>
     </row>
     <row r="28">
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.500185</v>
+        <v>-0.503129</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-4.089117</v>
+        <v>-4.188453</v>
       </c>
     </row>
     <row r="30">
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.675222</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>5.542504</v>
       </c>
     </row>
     <row r="35">
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.2875</v>
+        <v>1.962722</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.3125</v>
+        <v>5.855004</v>
       </c>
     </row>
     <row r="37">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.697233</v>
+        <v>0.022011</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>5.904207</v>
+        <v>0.361703</v>
       </c>
     </row>
     <row r="49">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
